--- a/r5-TC-FHIR-AG-Scheduling-R5-6-initial-OperationDefinitions/StructureDefinition-at-scheduling-schedule.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-6-initial-OperationDefinitions/StructureDefinition-at-scheduling-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-11T13:21:50+00:00</t>
+    <t>2025-01-18T13:02:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-6-initial-OperationDefinitions/StructureDefinition-at-scheduling-schedule.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-6-initial-OperationDefinitions/StructureDefinition-at-scheduling-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-18T13:02:21+00:00</t>
+    <t>2025-01-18T13:24:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-6-initial-OperationDefinitions/StructureDefinition-at-scheduling-schedule.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-6-initial-OperationDefinitions/StructureDefinition-at-scheduling-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-18T13:24:49+00:00</t>
+    <t>2025-01-18T13:45:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-6-initial-OperationDefinitions/StructureDefinition-at-scheduling-schedule.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-6-initial-OperationDefinitions/StructureDefinition-at-scheduling-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-18T13:45:55+00:00</t>
+    <t>2025-01-18T14:38:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-6-initial-OperationDefinitions/StructureDefinition-at-scheduling-schedule.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-6-initial-OperationDefinitions/StructureDefinition-at-scheduling-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-18T14:38:52+00:00</t>
+    <t>2025-01-25T14:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
